--- a/MechanismOfAction/bcio_moa.xlsx
+++ b/MechanismOfAction/bcio_moa.xlsx
@@ -4809,7 +4809,7 @@
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
       <c r="J75" s="3" t="n"/>
-      <c r="K75" s="3" t="inlineStr"/>
+      <c r="K75" s="3" t="n"/>
       <c r="L75" s="3" t="n"/>
       <c r="M75" s="3" t="n"/>
       <c r="N75" s="3" t="n"/>
@@ -28367,7 +28367,11 @@
           <t>personal capability</t>
         </is>
       </c>
-      <c r="C469" t="inlineStr"/>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>A bodily disposition whose realization ordinarily brings benefits to an organism or group of organisms, where "ordinarily" means within a typical range or context.</t>
+        </is>
+      </c>
       <c r="D469" t="inlineStr">
         <is>
           <t>bodily disposition</t>

--- a/MechanismOfAction/bcio_moa.xlsx
+++ b/MechanismOfAction/bcio_moa.xlsx
@@ -28122,7 +28122,7 @@
       </c>
       <c r="D465" s="3" t="inlineStr">
         <is>
-          <t>belief</t>
+          <t>belief about ones social environment</t>
         </is>
       </c>
       <c r="E465" s="3" t="n"/>

--- a/MechanismOfAction/bcio_moa.xlsx
+++ b/MechanismOfAction/bcio_moa.xlsx
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n"/>
+      <c r="F5" s="3" t="inlineStr"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="inlineStr">
@@ -15980,7 +15980,7 @@
       </c>
       <c r="L260" s="3" t="n"/>
       <c r="M260" s="3" t="n"/>
-      <c r="N260" s="3" t="n"/>
+      <c r="N260" s="3" t="inlineStr"/>
       <c r="O260" s="3" t="n"/>
       <c r="P260" s="3" t="n"/>
       <c r="Q260" s="3" t="n"/>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="E389" s="3" t="n"/>
-      <c r="F389" s="3" t="n"/>
+      <c r="F389" s="3" t="inlineStr"/>
       <c r="G389" s="3" t="n"/>
       <c r="H389" s="3" t="n"/>
       <c r="I389" s="3" t="n"/>
@@ -23654,7 +23654,7 @@
       <c r="K389" s="3" t="n"/>
       <c r="L389" s="3" t="inlineStr">
         <is>
-          <t>stimulus</t>
+          <t>stimulus; behavioural cue; external stimulus; reminder stimulus; extrinsic reward; internal stimulus; internal stimulus for behaviour; mental stimulus for behaviour; intrinsic reward</t>
         </is>
       </c>
       <c r="M389" s="3" t="n"/>
@@ -27698,32 +27698,32 @@
           <t>self-efficacy belief</t>
         </is>
       </c>
-      <c r="E458" s="4" t="inlineStr"/>
-      <c r="F458" s="4" t="inlineStr"/>
-      <c r="G458" s="4" t="inlineStr"/>
-      <c r="H458" s="4" t="inlineStr"/>
-      <c r="I458" s="4" t="inlineStr"/>
-      <c r="J458" s="4" t="inlineStr"/>
-      <c r="K458" s="4" t="inlineStr"/>
-      <c r="L458" s="4" t="inlineStr"/>
-      <c r="M458" s="4" t="inlineStr"/>
-      <c r="N458" s="4" t="inlineStr"/>
-      <c r="O458" s="4" t="inlineStr"/>
-      <c r="P458" s="4" t="inlineStr"/>
-      <c r="Q458" s="4" t="inlineStr"/>
-      <c r="R458" s="4" t="inlineStr"/>
+      <c r="E458" s="4" t="n"/>
+      <c r="F458" s="4" t="n"/>
+      <c r="G458" s="4" t="n"/>
+      <c r="H458" s="4" t="n"/>
+      <c r="I458" s="4" t="n"/>
+      <c r="J458" s="4" t="n"/>
+      <c r="K458" s="4" t="n"/>
+      <c r="L458" s="4" t="n"/>
+      <c r="M458" s="4" t="n"/>
+      <c r="N458" s="4" t="n"/>
+      <c r="O458" s="4" t="n"/>
+      <c r="P458" s="4" t="n"/>
+      <c r="Q458" s="4" t="n"/>
+      <c r="R458" s="4" t="n"/>
       <c r="S458" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="T458" s="4" t="inlineStr"/>
-      <c r="U458" s="4" t="inlineStr"/>
-      <c r="V458" s="4" t="inlineStr"/>
+      <c r="T458" s="4" t="n"/>
+      <c r="U458" s="4" t="n"/>
+      <c r="V458" s="4" t="n"/>
       <c r="W458" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="X458" s="4" t="inlineStr"/>
+      <c r="X458" s="4" t="n"/>
     </row>
     <row r="459">
       <c r="A459" s="3" t="inlineStr">

--- a/MechanismOfAction/bcio_moa.xlsx
+++ b/MechanismOfAction/bcio_moa.xlsx
@@ -751,7 +751,7 @@
         </is>
       </c>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="inlineStr"/>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n"/>
       <c r="H5" s="3" t="n"/>
       <c r="I5" s="3" t="inlineStr">
@@ -15980,7 +15980,7 @@
       </c>
       <c r="L260" s="3" t="n"/>
       <c r="M260" s="3" t="n"/>
-      <c r="N260" s="3" t="inlineStr"/>
+      <c r="N260" s="3" t="n"/>
       <c r="O260" s="3" t="n"/>
       <c r="P260" s="3" t="n"/>
       <c r="Q260" s="3" t="n"/>
@@ -21691,7 +21691,7 @@
       </c>
       <c r="D358" s="3" t="inlineStr">
         <is>
-          <t>learned stimulus-reponse co-occurrence</t>
+          <t>learned stimulus-response co-occurrence</t>
         </is>
       </c>
       <c r="E358" s="3" t="n"/>
@@ -21751,7 +21751,7 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>learned stimulus-reponse co-occurrence</t>
+          <t>learned stimulus-response co-occurrence</t>
         </is>
       </c>
       <c r="C359" s="3" t="inlineStr">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="D360" s="3" t="inlineStr">
         <is>
-          <t>learned stimulus-reponse co-occurrence</t>
+          <t>learned stimulus-response co-occurrence</t>
         </is>
       </c>
       <c r="E360" s="3" t="n"/>
@@ -23008,7 +23008,7 @@
       </c>
       <c r="L379" s="3" t="inlineStr">
         <is>
-          <t>bodily disposition</t>
+          <t>behavioural disposition; willingness to change behaviour; willingness to cease behaviour; willingness to adopt new behaviours; internal influence on behaviour; motivational disposition; motivational orientation; prevention focused motivational orientation; promotion focused motivational orientation; motivational disposition not to change behaviour; motivational disposition for behavioural maintenance; motivational disposition to change behaviour; behavioural capability; social behavioural capability; social skill; communication skill; assertiveness skill; negotiating skill; control over behaviour; psychological behavioural capability; physical behavioural capability; physical skill; mental disposition; awareness; awareness of standards; awareness of mortality; awareness of others’ need; cognitive bias disposition	; generality of self-efficacy; mental plan; mental plan for a behaviour; mental plan for coping with barriers; impulsive disposition; attentional disposition; disposition to attend to one’s goals; psychological attachment; psychological attachment to conventional society; attachment to a caregiver; belief; evaluative belief; evaluative belief about others; evaluative belief about achieving a goal; positive evaluative belief about achieving a goal; evaluative belief about a behaviour; positive evaluative belief about a behaviour; positive evaluative belief about interacting with others; negative evaluative belief about a behaviour; evaluation of self; belief about barriers to a behaviour; belief about effort required for a behaviour; belief about enablers of a behaviour; belief about susceptibility to a threat; belief about personal susceptibility; belief about others' susceptibility; belief about consequences of an occurrence; belief about consequences of goal attainment; 	belief about emotional consequences of goal attainment; belief about anticipated emotion; belief about anticipated regret; belief about likelihood of consequences of an occurrence; belief about likelihood of consequences of behaviour	; belief about likelihood of emotional consequences of behaviour; coping efficacy belief; belief about likelihood of social consequences of behaviour; belief about likelihood of health consequences of behaviour; belief about likelihood of financial consequences of a behaviour; belief about consequences of behaviour; belief about emotional consequences of behaviour; belief about the positive emotional consequences of a behaviour; belief about social consequences of behaviour; belief about the positive social consequences of a behaviour; belief about the timing of the consequences of behaviour; belief about health consequences of behaviour; belief about the negative health consequences of a behaviour; belief about the positive health consequences of a behaviour; evaluative belief about the consequences of behaviour	; evaluative belief about the positive consequences of a behaviour; evaluative belief about the negative consequences of a behaviour; belief about the personal desirability of consequences of a behaviour; belief about a behaviour meeting a need; evaluative belief about the consequences of one’s behaviour; belief about the financial consequences of a behaviour; belief about choice over a behaviour; belief about gain; belief about health status; belief about severity of an outcome; belief about severity of health condition; belief about severity of AIDS; belief about conformity of behaviour to personal values; self-efficacy belief; self-efficacy belief for a behaviour; behaviour maintenance self-efficacy; behavioural recovery self-efficacy; situational self-efficacy belief for a behaviour; self-efficacy belief for a behaviour in the face of social pressure; self-efficacy belief for a behaviour under conditions of stress; 	self-efficacy belief for a behaviour during routine activities; self-efficacy belief for avoiding a threat; self-efficacy belief for a behaviour and its associated outcomes; belief about goal attainment; denial belief; denial belief about a need; denial belief about norm relevance; denial belief about a responsibility to act; belief about the cause of a behaviour; external attribution of a behaviour; internal attribution of a behaviour; perceived norm; normative belief; perceived descriptive behavioural norm; underestimated perceived descriptive norm; overestimated perceived descriptive norm; perceived evaluative behavioural norm; belief about need satisfaction; belief about own health; belief about ones environment; belief about ones physical environment; belief about ones social environment; belief about social support; belief about social support for a behaviour; belief about social influence; belief about social influence on oneself; belief about healthcare accessibility; belief about sufficient time for a behaviour; belief about task complexity; belief about responsibility; belief about accountability for the consequences of an action; belief about responsibility to act; 	belief about reduction; belief about control over one's future; efficacy belief for a behaviour and its associated outcomes; belief about quality of life; belief about message; belief about the credibility of a message's source; belief about message relevance; belief about message trustworthiness; belief about threat; belief about a behavioural rule; belief that a behaviour is forbidden; belief that a behaviour is compulsory; belief about control over behaviour; belief about control over valued outcomes; external locus of control; internal locus of control; belief about conformity to behavioural norms; belief about the discrepancy between one’s current and target state; depressive disposition; cognitive schema; stereotype; risk-taker stereotype; action schema; personal value; egoistic personal value; egoistic personal health value; openness-to-change personal value; moral personal value; pro-environmental personal value; societal personal value; traditional personal value; social embeddedness; social embeddedness in a social group; psychological need; aesthetic appreciation disposition; need for autonomy; need for access to space; need for a sense of safety	; need for self-esteem; need for appreciation by others; need for privacy; need to hold a world view; need for a sense of belonging and attachment; need for natural environment; need for social justice; need to feel competent; need for comfort; behavioural intention; intention to enact a behaviour; intention not to enact a behaviour; intention for collective behaviour; resilience of self-efficacy; addiction; learned stimulus-response co-occurrence; learned stimulus-behaviour co-occurrence; learned stimulus-thought co-occurrence; decision; behavioural decision; utility maximisation disposition; positive mental health; misperception of descriptive behavioural norm; mental imagery disposition; attitude; attitude towards a behaviour; affective attitude towards a behaviour; affective attitude; affective attitude acquired through association; knowledge; knowledge regarding one's environment; knowledge regarding social environment; knowledge regarding a behaviour; knowledge regarding goal attainment; knowledge regarding an innovation; knowledge regarding a threat; knowledge about threat avoidance; knowledge regarding treatment; temporal orientation; temporal orientation to the present; temporal orientation to the future; social alienation; disengagement due to workload; total internal influence on behaviour; personal capability; mental capability; self-regulation capability; attentional self-regulation capability; self-regulatory skill; cognitive self-regulation capability; behavioural self-regulation capability; behavioural substitution capability; emotional self-regulation capability; imagination capability; capability to imagine future scenarios; mental skill; symbol processing skill; empathy; reflective capability; creative thinking; observational learning capability; vicarious learning capability; physiological need; substance dependence; emotional action tendency; bodily disposition that increases likelihood of harmful behaviour</t>
         </is>
       </c>
       <c r="M379" s="3" t="n"/>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="E389" s="3" t="n"/>
-      <c r="F389" s="3" t="inlineStr"/>
+      <c r="F389" s="3" t="n"/>
       <c r="G389" s="3" t="n"/>
       <c r="H389" s="3" t="n"/>
       <c r="I389" s="3" t="n"/>

--- a/MechanismOfAction/bcio_moa.xlsx
+++ b/MechanismOfAction/bcio_moa.xlsx
@@ -23126,7 +23126,7 @@
         </is>
       </c>
       <c r="E381" s="3" t="n"/>
-      <c r="F381" s="3" t="n"/>
+      <c r="F381" s="3" t="inlineStr"/>
       <c r="G381" s="3" t="n"/>
       <c r="H381" s="3" t="n"/>
       <c r="I381" s="3" t="n"/>
@@ -23144,7 +23144,7 @@
       </c>
       <c r="L381" s="3" t="inlineStr">
         <is>
-          <t>cognitive representation</t>
+          <t>cognitive representation; cognitive representation of one’s behaviour; cognitive representation of an alternative behaviour	; goal; well-specified goal; self-initiated goal; assigned goal; learning goal; active goal; accepted assigned goal; goal about one’s resources; proximal goal; hedonic goal; behavioural goal; normative goal; collaborative goal; distal goal; background goal; desired standard; desired standard for self-identity; desired self-regulatory standard; social representation of a behaviour; propositional cognitive representation; identity; group identity; self-identity; professional identity; social identity	; similarity to other people; affective appraisal; behavioural consequence appraisal process; social consequence of behaviour appraisal process; appraisal of goal importance; appraisal of expectedness; appraisal of desirability; appraisal of desirability of consequences; appraisal of obligation to act; appraisal of immediacy; appraisal of pleasantness; appraisal of dangerousness; affective appraisal of possible consequences; self-identity appraisal process; self-identity appraisal informed by one’s behaviour; appraisal of social identity; appraisal of causal agency; appraisal as caused by external non-human factors; appraisal as caused by an other; appraisal as caused by self; appraisal of avoidability of consequences; comparative desirability appraisal; mental image</t>
         </is>
       </c>
       <c r="M381" s="3" t="n"/>
@@ -23193,7 +23193,7 @@
           <t>behaviour change intervention mechanism of action</t>
         </is>
       </c>
-      <c r="E382" s="3" t="inlineStr"/>
+      <c r="E382" s="3" t="n"/>
       <c r="F382" s="3" t="n"/>
       <c r="G382" s="3" t="n"/>
       <c r="H382" s="3" t="n"/>
@@ -23536,7 +23536,7 @@
       </c>
       <c r="L387" s="3" t="n"/>
       <c r="M387" s="3" t="n"/>
-      <c r="N387" s="3" t="inlineStr"/>
+      <c r="N387" s="3" t="n"/>
       <c r="O387" s="3" t="n"/>
       <c r="P387" s="3" t="n"/>
       <c r="Q387" s="3" t="n"/>
@@ -23655,7 +23655,7 @@
 In this definition, ‘change’ refers to change from what would have been the case rather than change from an existing state of affairs. This is to capture the fact that mechanisms of action can act to sustain a current state of affairs, for example preventing smoking uptake. In the definition, ‘some change’ captures changes in salience, change in valence, or being added, increased, decreased, manifested/realised, created, started, stopped or altered rate.</t>
         </is>
       </c>
-      <c r="K389" s="3" t="inlineStr"/>
+      <c r="K389" s="3" t="n"/>
       <c r="L389" s="3" t="inlineStr">
         <is>
           <t>stimulus; behavioural cue; external stimulus; reminder stimulus; extrinsic reward; internal stimulus; internal stimulus for behaviour; mental stimulus for behaviour; intrinsic reward</t>
